--- a/ig/DM-37/ValueSet-JDV-J221-NatureContact-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J221-NatureContact-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>Téléexpertise</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Cellule opérationnelle de Bed Management</t>
   </si>
   <si>
     <t/>
@@ -471,7 +477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -611,15 +617,23 @@
         <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
